--- a/Auditmarks.xlsx
+++ b/Auditmarks.xlsx
@@ -1431,7 +1431,7 @@
         <v>C2</v>
       </c>
       <c r="G45" t="str">
-        <v>XLIV</v>
+        <v>XLVIII</v>
       </c>
     </row>
     <row r="46">
@@ -1454,7 +1454,7 @@
         <v>C1</v>
       </c>
       <c r="G46" t="str">
-        <v>XXIX</v>
+        <v>XXXI</v>
       </c>
     </row>
     <row r="47">
@@ -1500,7 +1500,7 @@
         <v>C2</v>
       </c>
       <c r="G48" t="str">
-        <v>XXXVIII</v>
+        <v>XLI</v>
       </c>
     </row>
     <row r="49">
@@ -1523,7 +1523,7 @@
         <v>B1</v>
       </c>
       <c r="G49" t="str">
-        <v>VII</v>
+        <v>VIII</v>
       </c>
     </row>
     <row r="50">
@@ -1546,7 +1546,7 @@
         <v>E</v>
       </c>
       <c r="G50" t="str">
-        <v>LI</v>
+        <v>LVII</v>
       </c>
     </row>
     <row r="51">
@@ -1569,7 +1569,7 @@
         <v>D</v>
       </c>
       <c r="G51" t="str">
-        <v>XLVIII</v>
+        <v>LIII</v>
       </c>
     </row>
     <row r="52">
@@ -1592,7 +1592,7 @@
         <v>B1</v>
       </c>
       <c r="G52" t="str">
-        <v>V</v>
+        <v>VI</v>
       </c>
     </row>
     <row r="53">
@@ -1615,7 +1615,7 @@
         <v>C1</v>
       </c>
       <c r="G53" t="str">
-        <v>XXXI</v>
+        <v>XXXII</v>
       </c>
     </row>
     <row r="54">
@@ -1638,7 +1638,7 @@
         <v>C2</v>
       </c>
       <c r="G54" t="str">
-        <v>XXXIV</v>
+        <v>XXXVII</v>
       </c>
     </row>
     <row r="55">
@@ -1661,7 +1661,7 @@
         <v>B2</v>
       </c>
       <c r="G55" t="str">
-        <v>XVIII</v>
+        <v>XX</v>
       </c>
     </row>
     <row r="56">
@@ -1684,7 +1684,7 @@
         <v>C2</v>
       </c>
       <c r="G56" t="str">
-        <v>-</v>
+        <v>XLIII</v>
       </c>
     </row>
     <row r="57">
@@ -1707,7 +1707,7 @@
         <v>D</v>
       </c>
       <c r="G57" t="str">
-        <v>-</v>
+        <v>LII</v>
       </c>
     </row>
     <row r="58">
@@ -1730,7 +1730,7 @@
         <v>C1</v>
       </c>
       <c r="G58" t="str">
-        <v>XXV</v>
+        <v>XXVII</v>
       </c>
     </row>
     <row r="59">
@@ -1753,7 +1753,7 @@
         <v>D</v>
       </c>
       <c r="G59" t="str">
-        <v>L</v>
+        <v>LVI</v>
       </c>
     </row>
     <row r="60">
@@ -1776,7 +1776,7 @@
         <v>B2</v>
       </c>
       <c r="G60" t="str">
-        <v>XVII</v>
+        <v>XVIII</v>
       </c>
     </row>
     <row r="61">
@@ -1799,7 +1799,7 @@
         <v>C2</v>
       </c>
       <c r="G61" t="str">
-        <v>XXXIX</v>
+        <v>XLII</v>
       </c>
     </row>
     <row r="62">
@@ -1822,7 +1822,7 @@
         <v>C1</v>
       </c>
       <c r="G62" t="str">
-        <v>XXIV</v>
+        <v>XXVI</v>
       </c>
     </row>
     <row r="63">
@@ -1845,7 +1845,7 @@
         <v>E</v>
       </c>
       <c r="G63" t="str">
-        <v>LII</v>
+        <v>LIX</v>
       </c>
     </row>
     <row r="64">
@@ -1868,7 +1868,7 @@
         <v>E</v>
       </c>
       <c r="G64" t="str">
-        <v>-</v>
+        <v>LVIII</v>
       </c>
     </row>
     <row r="65">
@@ -1914,7 +1914,7 @@
         <v>B2</v>
       </c>
       <c r="G66" t="str">
-        <v>-</v>
+        <v>XXI</v>
       </c>
     </row>
     <row r="67">
@@ -1937,7 +1937,7 @@
         <v>B1</v>
       </c>
       <c r="G67" t="str">
-        <v>IV</v>
+        <v>V</v>
       </c>
     </row>
     <row r="68">
@@ -1960,7 +1960,7 @@
         <v>C1</v>
       </c>
       <c r="G68" t="str">
-        <v>XXIII</v>
+        <v>XXV</v>
       </c>
     </row>
     <row r="69">
@@ -2006,7 +2006,7 @@
         <v>C1</v>
       </c>
       <c r="G70" t="str">
-        <v>XXVII</v>
+        <v>XXIX</v>
       </c>
     </row>
     <row r="71">
@@ -2029,7 +2029,7 @@
         <v>C2</v>
       </c>
       <c r="G71" t="str">
-        <v>XXXIII</v>
+        <v>XXXVI</v>
       </c>
     </row>
     <row r="72">
@@ -2052,7 +2052,7 @@
         <v>D</v>
       </c>
       <c r="G72" t="str">
-        <v>XLIX</v>
+        <v>LV</v>
       </c>
     </row>
     <row r="73">
@@ -2075,7 +2075,7 @@
         <v>C1</v>
       </c>
       <c r="G73" t="str">
-        <v>XXII</v>
+        <v>XXIV</v>
       </c>
     </row>
     <row r="74">
@@ -2098,7 +2098,7 @@
         <v>B1</v>
       </c>
       <c r="G74" t="str">
-        <v>VIII</v>
+        <v>IX</v>
       </c>
     </row>
     <row r="75">
@@ -2144,7 +2144,7 @@
         <v>A2</v>
       </c>
       <c r="G76" t="str">
-        <v>I</v>
+        <v>II</v>
       </c>
     </row>
     <row r="77">
@@ -2167,7 +2167,7 @@
         <v>D</v>
       </c>
       <c r="G77" t="str">
-        <v>XLVI</v>
+        <v>L</v>
       </c>
     </row>
     <row r="78">
@@ -2190,7 +2190,7 @@
         <v>B2</v>
       </c>
       <c r="G78" t="str">
-        <v>XX</v>
+        <v>XXII</v>
       </c>
     </row>
     <row r="79">
@@ -2213,7 +2213,7 @@
         <v>B1</v>
       </c>
       <c r="G79" t="str">
-        <v>IX</v>
+        <v>X</v>
       </c>
     </row>
     <row r="80">
@@ -2236,7 +2236,7 @@
         <v>C2</v>
       </c>
       <c r="G80" t="str">
-        <v>XLIII</v>
+        <v>XLVI</v>
       </c>
     </row>
     <row r="81">
@@ -2259,7 +2259,7 @@
         <v>C1</v>
       </c>
       <c r="G81" t="str">
-        <v>XXXIII</v>
+        <v>XXXV</v>
       </c>
     </row>
     <row r="82">
@@ -2282,7 +2282,7 @@
         <v>A2</v>
       </c>
       <c r="G82" t="str">
-        <v>-</v>
+        <v>III</v>
       </c>
     </row>
     <row r="83">
@@ -2328,7 +2328,7 @@
         <v>C2</v>
       </c>
       <c r="G84" t="str">
-        <v>XLV</v>
+        <v>XLIX</v>
       </c>
     </row>
     <row r="85">
@@ -2374,7 +2374,7 @@
         <v>C2</v>
       </c>
       <c r="G86" t="str">
-        <v>XLII</v>
+        <v>XLV</v>
       </c>
     </row>
     <row r="87">
@@ -2397,7 +2397,7 @@
         <v>C1</v>
       </c>
       <c r="G87" t="str">
-        <v>XXIX</v>
+        <v>XXX</v>
       </c>
     </row>
     <row r="88">
@@ -2420,7 +2420,7 @@
         <v>C1</v>
       </c>
       <c r="G88" t="str">
-        <v>-</v>
+        <v>XXIII</v>
       </c>
     </row>
     <row r="89">
@@ -2443,7 +2443,7 @@
         <v>D</v>
       </c>
       <c r="G89" t="str">
-        <v>-</v>
+        <v>LIV</v>
       </c>
     </row>
     <row r="90">
@@ -2466,7 +2466,7 @@
         <v>A2</v>
       </c>
       <c r="G90" t="str">
-        <v>X</v>
+        <v>I</v>
       </c>
     </row>
     <row r="91">
@@ -2489,7 +2489,7 @@
         <v>C2</v>
       </c>
       <c r="G91" t="str">
-        <v>XXXVII</v>
+        <v>XXXIX</v>
       </c>
     </row>
     <row r="92">
@@ -2512,7 +2512,7 @@
         <v>B1</v>
       </c>
       <c r="G92" t="str">
-        <v>II</v>
+        <v>IV</v>
       </c>
     </row>
     <row r="93">
@@ -2535,7 +2535,7 @@
         <v>D</v>
       </c>
       <c r="G93" t="str">
-        <v>XLVII</v>
+        <v>LI</v>
       </c>
     </row>
     <row r="94">
@@ -2558,7 +2558,7 @@
         <v>C1</v>
       </c>
       <c r="G94" t="str">
-        <v>XIX</v>
+        <v>XXI</v>
       </c>
     </row>
     <row r="95">
@@ -2581,7 +2581,7 @@
         <v>C1</v>
       </c>
       <c r="G95" t="str">
-        <v>-</v>
+        <v>XXXIII</v>
       </c>
     </row>
     <row r="96">
@@ -2604,7 +2604,7 @@
         <v>B2</v>
       </c>
       <c r="G96" t="str">
-        <v>-</v>
+        <v>XVII</v>
       </c>
     </row>
     <row r="97">
@@ -2627,7 +2627,7 @@
         <v>B2</v>
       </c>
       <c r="G97" t="str">
-        <v>-</v>
+        <v>XIX</v>
       </c>
     </row>
     <row r="98">
@@ -2650,7 +2650,7 @@
         <v>C2</v>
       </c>
       <c r="G98" t="str">
-        <v>XLI</v>
+        <v>XLIV</v>
       </c>
     </row>
     <row r="99">
@@ -2673,7 +2673,7 @@
         <v>C1</v>
       </c>
       <c r="G99" t="str">
-        <v>XXXII</v>
+        <v>XXXIV</v>
       </c>
     </row>
     <row r="100">
@@ -2696,7 +2696,7 @@
         <v>C2</v>
       </c>
       <c r="G100" t="str">
-        <v>XXXV</v>
+        <v>XXXVIII</v>
       </c>
     </row>
     <row r="101">
@@ -2719,7 +2719,7 @@
         <v>B1</v>
       </c>
       <c r="G101" t="str">
-        <v>VI</v>
+        <v>VII</v>
       </c>
     </row>
     <row r="102">
@@ -2742,7 +2742,7 @@
         <v>C2</v>
       </c>
       <c r="G102" t="str">
-        <v>XXXVII</v>
+        <v>XL</v>
       </c>
     </row>
     <row r="103">
@@ -2788,7 +2788,7 @@
         <v>C2</v>
       </c>
       <c r="G104" t="str">
-        <v>-</v>
+        <v>XLVII</v>
       </c>
     </row>
     <row r="105">
@@ -2811,7 +2811,7 @@
         <v>C1</v>
       </c>
       <c r="G105" t="str">
-        <v>XXVI</v>
+        <v>XXVIII</v>
       </c>
     </row>
     <row r="106">
